--- a/artfynd/Lögdeälven artfynd.xlsx
+++ b/artfynd/Lögdeälven artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>14247440</v>
+        <v>1989107</v>
       </c>
       <c r="B2" t="n">
-        <v>5492</v>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101410</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>13 km SV om Västra Örtträsk, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>681435</v>
+        <v>681383</v>
       </c>
       <c r="R2" t="n">
-        <v>7109642</v>
+        <v>7108938</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2005-08-17</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2005-07-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2005-08-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2005-07-05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Sveaskog Västerbotten</t>
+          <t>Via Daniella Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1989107</v>
+        <v>1988825</v>
       </c>
       <c r="B3" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>681383</v>
+        <v>681111</v>
       </c>
       <c r="R3" t="n">
-        <v>7108938</v>
+        <v>7109646</v>
       </c>
       <c r="S3" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2005-07-05</t>
+          <t>2005-07-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2005-07-05</t>
+          <t>2005-07-01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,12 +857,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Sveaskog Västerbotten</t>
+          <t>Via Daniella Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -887,7 +872,7 @@
         <v>14247445</v>
       </c>
       <c r="B4" t="n">
-        <v>5492</v>
+        <v>5495</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -957,19 +942,9 @@
           <t>2005-08-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2005-08-16</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,103 +968,6 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>1988825</v>
-      </c>
-      <c r="B5" t="n">
-        <v>80083</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>13 km SV om Västra Örtträsk, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>681111</v>
-      </c>
-      <c r="R5" t="n">
-        <v>7109646</v>
-      </c>
-      <c r="S5" t="n">
-        <v>100</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Fredrika</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2005-07-01</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2005-07-01</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Sveaskog Västerbotten</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Via Sveaskog Västerbotten</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
